--- a/reports/FR-17_domain_test_cases.xlsx
+++ b/reports/FR-17_domain_test_cases.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="209">
   <si>
     <t>ID</t>
   </si>
@@ -601,9 +601,6 @@
     <t>Không phải kiểu số</t>
   </si>
   <si>
-    <t>Không phải số nguyên</t>
-  </si>
-  <si>
     <t>Nhập '10.5'</t>
   </si>
   <si>
@@ -635,6 +632,27 @@
   </si>
   <si>
     <t>Rejected; 'max_uses_per_user' phải kiểu số</t>
+  </si>
+  <si>
+    <t>TC-FR17-29</t>
+  </si>
+  <si>
+    <t>TC-FR17-30</t>
+  </si>
+  <si>
+    <t>TC-FR17-31</t>
+  </si>
+  <si>
+    <t>TC-FR17-32</t>
+  </si>
+  <si>
+    <t>TC-FR17-33</t>
+  </si>
+  <si>
+    <t>TC-FR17-34</t>
+  </si>
+  <si>
+    <t>Số thực</t>
   </si>
 </sst>
 </file>
@@ -709,7 +727,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -735,7 +753,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1852,18 +1869,20 @@
       <c r="I29" s="6"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
+      <c r="A30" s="4" t="s">
+        <v>202</v>
+      </c>
       <c r="B30" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>192</v>
-      </c>
       <c r="E30" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>177</v>
@@ -1871,45 +1890,53 @@
       <c r="G30" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="H30" s="4"/>
+      <c r="H30" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="I30" s="6"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
+      <c r="A31" s="4" t="s">
+        <v>203</v>
+      </c>
       <c r="B31" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="F31" s="10" t="s">
+      <c r="D31" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="F31" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="H31" s="9"/>
-      <c r="I31" s="11"/>
+      <c r="G31" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="10"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
+      <c r="A32" s="4" t="s">
+        <v>204</v>
+      </c>
       <c r="B32" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>194</v>
+        <v>208</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>193</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>177</v>
@@ -1917,77 +1944,91 @@
       <c r="G32" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="H32" s="9"/>
-      <c r="I32" s="11"/>
+      <c r="H32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="10"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
+      <c r="A33" s="4" t="s">
+        <v>205</v>
+      </c>
       <c r="B33" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="F33" s="10" t="s">
+      <c r="D33" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="F33" s="9" t="s">
         <v>180</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="H33" s="9"/>
-      <c r="I33" s="11"/>
+      <c r="H33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="10"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
+      <c r="A34" s="4" t="s">
+        <v>206</v>
+      </c>
       <c r="B34" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="F34" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="F34" s="9" t="s">
         <v>180</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="H34" s="9"/>
-      <c r="I34" s="11"/>
+      <c r="H34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
+      <c r="A35" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="B35" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D35" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="F35" s="10" t="s">
+      <c r="D35" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F35" s="9" t="s">
         <v>180</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="H35" s="9"/>
-      <c r="I35" s="11"/>
+      <c r="H35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I29"/>

--- a/reports/FR-17_domain_test_cases.xlsx
+++ b/reports/FR-17_domain_test_cases.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variables!$A$1:$D$10</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
